--- a/vendor/ironcalc/xlsx/tests/calc_tests/STATISTICAL/POISSON.xlsx
+++ b/vendor/ironcalc/xlsx/tests/calc_tests/STATISTICAL/POISSON.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nhatcher/Documents/Excel/Statistical/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elsam\Documents\IronCalc stuff\my_calc_tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98620EB5-AEAC-E34F-9148-61BA3242DD87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F649C0C2-ACD3-400B-BF15-7126F3A89D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8580" yWindow="1500" windowWidth="22240" windowHeight="17440" xr2:uid="{9C2F1A6F-3B02-154E-8A58-C47B6E22311E}"/>
+    <workbookView xWindow="5535" yWindow="1702" windowWidth="14925" windowHeight="10891" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="POISSON.DIST" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="70">
   <si>
     <t>x</t>
   </si>
@@ -45,30 +42,251 @@
   </si>
   <si>
     <t>cumulative</t>
+  </si>
+  <si>
+    <t>POISSON.DIST</t>
+  </si>
+  <si>
+    <t>NOTES</t>
+  </si>
+  <si>
+    <t>Documentation CDF example → 0.124652</t>
+  </si>
+  <si>
+    <t>Documentation PMF example → 0.084224</t>
+  </si>
+  <si>
+    <t>x = 0, CDF → P(X≤0) = e^−mean</t>
+  </si>
+  <si>
+    <t>x = 0, PMF → P(X=0) = e^−mean</t>
+  </si>
+  <si>
+    <t>x = mean, CDF</t>
+  </si>
+  <si>
+    <t>x = mean, PMF (mode)</t>
+  </si>
+  <si>
+    <t>mean = 1, x = 1 CDF</t>
+  </si>
+  <si>
+    <t>mean = 1, x = 1 PMF</t>
+  </si>
+  <si>
+    <t>mean = 0, x = 0 → P = 1 (CDF)</t>
+  </si>
+  <si>
+    <t>mean = 0, x = 0 → P = 1 (PMF)</t>
+  </si>
+  <si>
+    <t>x &gt;&gt; mean, CDF (tail)</t>
+  </si>
+  <si>
+    <t>x &gt;&gt; mean, PMF (rare event)</t>
+  </si>
+  <si>
+    <t>Very small mean (near 0)</t>
+  </si>
+  <si>
+    <t>Large x = mean</t>
+  </si>
+  <si>
+    <t>x &gt; large mean, CDF near 1</t>
+  </si>
+  <si>
+    <t>Non-integer x (2.9 truncated to 2)</t>
+  </si>
+  <si>
+    <t>Non-integer x (2.1 truncated to 2)</t>
+  </si>
+  <si>
+    <t>Non-integer x, PMF (2.9 → 2)</t>
+  </si>
+  <si>
+    <t>Non-integer x &lt; 1 (0.9 truncated to 0)</t>
+  </si>
+  <si>
+    <t>Very large mean</t>
+  </si>
+  <si>
+    <t>Very large x = mean</t>
+  </si>
+  <si>
+    <t>x &lt; 0 → #NUM!</t>
+  </si>
+  <si>
+    <t>mean &lt; 0 → #NUM!</t>
+  </si>
+  <si>
+    <t>Both negative → #NUM!</t>
+  </si>
+  <si>
+    <t>Empty x</t>
+  </si>
+  <si>
+    <t>Empty mean</t>
+  </si>
+  <si>
+    <t>Empty cumulative</t>
+  </si>
+  <si>
+    <t>Error propagation – DIV/0 in x</t>
+  </si>
+  <si>
+    <t>Error propagation – NA in mean</t>
+  </si>
+  <si>
+    <t>Error propagation – DIV/0 in cumulative</t>
+  </si>
+  <si>
+    <t>x as TRUE (→ 1)</t>
+  </si>
+  <si>
+    <t>x as FALSE (→ 0)</t>
+  </si>
+  <si>
+    <t>mean as TRUE (→ 1)</t>
+  </si>
+  <si>
+    <t>cumulative as number 1</t>
+  </si>
+  <si>
+    <t>cumulative as number 0</t>
+  </si>
+  <si>
+    <t>cumulative as invalid number</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>cumulative as string "TRUE"</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>cumulative as lowercase string</t>
+  </si>
+  <si>
+    <t>"TRUE"</t>
+  </si>
+  <si>
+    <t>cumulative as quoted string</t>
+  </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>cumulative as invalid string</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>x as numeric text string</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>mean as numeric text string</t>
+  </si>
+  <si>
+    <t>"2"</t>
+  </si>
+  <si>
+    <t>x as quoted numeric string</t>
+  </si>
+  <si>
+    <t>hi</t>
+  </si>
+  <si>
+    <t>x as non-numeric text → #VALUE!</t>
+  </si>
+  <si>
+    <t>Date as x (serial ≈ 45675)</t>
+  </si>
+  <si>
+    <t>Empty x (direct)</t>
+  </si>
+  <si>
+    <t>Empty mean (direct)</t>
+  </si>
+  <si>
+    <t>Empty cumulative (direct)</t>
+  </si>
+  <si>
+    <t>All empty (direct)</t>
+  </si>
+  <si>
+    <t>Smoke test</t>
+  </si>
+  <si>
+    <t>mean = 0, x = 1 → P = 0 (PMF)</t>
+  </si>
+  <si>
+    <t>mean = 0, x = 1 → P = 0 (CDF)</t>
+  </si>
+  <si>
+    <t>x near zero</t>
+  </si>
+  <si>
+    <t>x near zero (negative)</t>
+  </si>
+  <si>
+    <t>mean near zero</t>
+  </si>
+  <si>
+    <t>mean near zero (negative)</t>
+  </si>
+  <si>
+    <t>Implicit intersection</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -76,18 +294,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -110,44 +349,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -174,32 +413,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -226,24 +447,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -255,212 +458,1265 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3583C86C-585A-884B-8E3F-D86BD8159CC0}">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G61"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="3" width="11.59765625" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
+    <col min="5" max="5" width="38.265625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="2">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <f t="shared" ref="D2:D55" si="0">_xlfn.POISSON.DIST(A2,B2,C2)</f>
+        <v>0.12465201948308113</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <f t="shared" si="0"/>
+        <v>8.4224337488568335E-2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="2">
         <v>0.7</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <f>_xlfn.POISSON.DIST(A2,B2,C2)</f>
+      <c r="B4" s="2">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <f t="shared" si="0"/>
         <v>0.1353352832366127</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3">
+      <c r="E4" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="2">
         <v>0.2</v>
       </c>
-      <c r="B3">
+      <c r="B5" s="2">
         <v>3</v>
       </c>
-      <c r="C3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <f>_xlfn.POISSON.DIST(A3,B3,C3)</f>
+      <c r="C5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <f t="shared" si="0"/>
         <v>4.9787068367863944E-2</v>
       </c>
+      <c r="E5" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="2">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3">
+        <f t="shared" si="0"/>
+        <v>6.737946999085467E-3</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="2">
+        <v>0</v>
+      </c>
+      <c r="B7" s="2">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <f t="shared" si="0"/>
+        <v>6.737946999085467E-3</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="2">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3">
+        <f t="shared" si="0"/>
+        <v>0.61596065483306306</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" s="2">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <f t="shared" si="0"/>
+        <v>0.17546736976785071</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" s="2">
+        <v>1</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3">
+        <f t="shared" si="0"/>
+        <v>0.73575888234288478</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" s="2">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <f t="shared" si="0"/>
+        <v>0.36787944117144233</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12" s="2">
+        <v>0</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A13" s="2">
+        <v>0</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A14" s="2">
+        <v>1</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A15" s="2">
+        <v>1</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <f t="shared" ref="D15" si="1">_xlfn.POISSON.DIST(A15,B15,C15)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A16" s="2">
+        <v>10</v>
+      </c>
+      <c r="B16" s="2">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3">
+        <f t="shared" si="0"/>
+        <v>0.98630473140161712</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" s="2">
+        <v>10</v>
+      </c>
+      <c r="B17" s="2">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <f t="shared" si="0"/>
+        <v>1.8132788707821874E-2</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" s="2">
+        <v>0</v>
+      </c>
+      <c r="B18" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="C18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99900049983337502</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A19" s="2">
+        <v>100</v>
+      </c>
+      <c r="B19" s="2">
+        <v>100</v>
+      </c>
+      <c r="C19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3">
+        <f t="shared" si="0"/>
+        <v>0.52656219852999842</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A20" s="2">
+        <v>200</v>
+      </c>
+      <c r="B20" s="2">
+        <v>100</v>
+      </c>
+      <c r="C20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A21" s="2">
+        <v>2.9999989999999999</v>
+      </c>
+      <c r="B21" s="2">
+        <v>5</v>
+      </c>
+      <c r="C21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3">
+        <f t="shared" si="0"/>
+        <v>0.12465201948308113</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A22" s="2">
+        <v>2.0000010000000001</v>
+      </c>
+      <c r="B22" s="2">
+        <v>5</v>
+      </c>
+      <c r="C22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3">
+        <f t="shared" si="0"/>
+        <v>0.12465201948308113</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A23" s="2">
+        <v>2.9999989999999999</v>
+      </c>
+      <c r="B23" s="2">
+        <v>5</v>
+      </c>
+      <c r="C23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3">
+        <f t="shared" si="0"/>
+        <v>8.4224337488568335E-2</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A24" s="2">
+        <v>0.99999899999999997</v>
+      </c>
+      <c r="B24" s="2">
+        <v>5</v>
+      </c>
+      <c r="C24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3">
+        <f t="shared" si="0"/>
+        <v>6.737946999085467E-3</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A25" s="4">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="B25" s="2">
+        <v>5</v>
+      </c>
+      <c r="C25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" s="3">
+        <f t="shared" si="0"/>
+        <v>6.737946999085467E-3</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A26" s="4">
+        <v>-9.9999999999999995E-7</v>
+      </c>
+      <c r="B26" s="2">
+        <v>5</v>
+      </c>
+      <c r="C26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A27" s="2">
+        <v>3</v>
+      </c>
+      <c r="B27" s="4">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="C27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A28" s="2">
+        <v>3</v>
+      </c>
+      <c r="B28" s="4">
+        <v>-9.9999999999999995E-7</v>
+      </c>
+      <c r="C28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A29" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="B29" s="2">
+        <v>5</v>
+      </c>
+      <c r="C29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A30" s="2">
+        <v>10</v>
+      </c>
+      <c r="B30" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="C30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A31" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="B31" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="C31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D31" s="3">
+        <f t="shared" si="0"/>
+        <v>0.50026596148628366</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A32" s="2">
+        <v>-1</v>
+      </c>
+      <c r="B32" s="2">
+        <v>5</v>
+      </c>
+      <c r="C32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A33" s="2">
+        <v>2</v>
+      </c>
+      <c r="B33" s="2">
+        <v>-1</v>
+      </c>
+      <c r="C33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D33" s="3" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A34" s="2">
+        <v>-1</v>
+      </c>
+      <c r="B34" s="2">
+        <v>-1</v>
+      </c>
+      <c r="C34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D34" s="3" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B35" s="2">
+        <v>5</v>
+      </c>
+      <c r="C35" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D35" s="3">
+        <f t="shared" si="0"/>
+        <v>6.737946999085467E-3</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A36" s="2">
+        <v>2</v>
+      </c>
+      <c r="C36" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D36" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A37" s="2">
+        <v>2</v>
+      </c>
+      <c r="B37" s="2">
+        <v>5</v>
+      </c>
+      <c r="D37" s="3">
+        <f t="shared" si="0"/>
+        <v>8.4224337488568335E-2</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A38" s="2" t="e">
+        <f>1/0</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="B38" s="2">
+        <v>5</v>
+      </c>
+      <c r="C38" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D38" s="3" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A39" s="2">
+        <v>2</v>
+      </c>
+      <c r="B39" s="2" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C39" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D39" s="3" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A40" s="2">
+        <v>2</v>
+      </c>
+      <c r="B40" s="2">
+        <v>5</v>
+      </c>
+      <c r="C40" s="2" t="e">
+        <f>1/0</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D40" s="3" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A41" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="B41" s="2">
+        <v>5</v>
+      </c>
+      <c r="C41" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D41" s="3">
+        <f t="shared" si="0"/>
+        <v>4.0427681994512799E-2</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A42" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="B42" s="2">
+        <v>5</v>
+      </c>
+      <c r="C42" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3">
+        <f t="shared" si="0"/>
+        <v>6.737946999085467E-3</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A43" s="2">
+        <v>2</v>
+      </c>
+      <c r="B43" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C43" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D43" s="3">
+        <f t="shared" si="0"/>
+        <v>0.91969860292860584</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A44" s="2">
+        <v>2</v>
+      </c>
+      <c r="B44" s="2">
+        <v>5</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1</v>
+      </c>
+      <c r="D44" s="3">
+        <f t="shared" si="0"/>
+        <v>0.12465201948308113</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A45" s="2">
+        <v>2</v>
+      </c>
+      <c r="B45" s="2">
+        <v>5</v>
+      </c>
+      <c r="C45" s="5">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3">
+        <f t="shared" si="0"/>
+        <v>8.4224337488568335E-2</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A46" s="2">
+        <v>2</v>
+      </c>
+      <c r="B46" s="2">
+        <v>5</v>
+      </c>
+      <c r="C46" s="5">
+        <v>6</v>
+      </c>
+      <c r="D46" s="3">
+        <f t="shared" si="0"/>
+        <v>0.12465201948308113</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A47" s="2">
+        <v>2</v>
+      </c>
+      <c r="B47" s="2">
+        <v>5</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D47" s="3">
+        <f t="shared" si="0"/>
+        <v>0.12465201948308113</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A48" s="2">
+        <v>2</v>
+      </c>
+      <c r="B48" s="2">
+        <v>5</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D48" s="3">
+        <f t="shared" si="0"/>
+        <v>0.12465201948308113</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A49" s="2">
+        <v>2</v>
+      </c>
+      <c r="B49" s="2">
+        <v>5</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D49" s="3" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A50" s="2">
+        <v>2</v>
+      </c>
+      <c r="B50" s="2">
+        <v>5</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D50" s="3" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A51" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" s="2">
+        <v>5</v>
+      </c>
+      <c r="C51" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D51" s="3">
+        <f t="shared" si="0"/>
+        <v>0.12465201948308113</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A52" s="2">
+        <v>2</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C52" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D52" s="3">
+        <f t="shared" si="0"/>
+        <v>0.12465201948308113</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A53" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" s="2">
+        <v>5</v>
+      </c>
+      <c r="C53" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D53" s="3" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A54" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" s="2">
+        <v>5</v>
+      </c>
+      <c r="C54" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D54" s="3" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A55" s="6">
+        <v>46040</v>
+      </c>
+      <c r="B55" s="6">
+        <v>46071</v>
+      </c>
+      <c r="C55" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D55" s="3">
+        <f t="shared" si="0"/>
+        <v>0.4438020698095389</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B56" s="2">
+        <v>5</v>
+      </c>
+      <c r="C56" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D56" s="3">
+        <f>_xlfn.POISSON.DIST(,B56,C56)</f>
+        <v>6.737946999085467E-3</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A57" s="2">
+        <v>2</v>
+      </c>
+      <c r="C57" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D57" s="3">
+        <f>_xlfn.POISSON.DIST(A57,,C57)</f>
+        <v>1</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A58" s="2">
+        <v>2</v>
+      </c>
+      <c r="B58" s="2">
+        <v>5</v>
+      </c>
+      <c r="D58" s="3">
+        <f>_xlfn.POISSON.DIST(A58,B58,)</f>
+        <v>8.4224337488568335E-2</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="D59" s="3">
+        <f>_xlfn.POISSON.DIST(,,)</f>
+        <v>1</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F59" s="2">
+        <v>0</v>
+      </c>
+      <c r="G59" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B60">
+        <v>2</v>
+      </c>
+      <c r="C60" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D60" s="3">
+        <f>_xlfn.POISSON.DIST(F:F,B60,C60)</f>
+        <v>0.6766764161830634</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F60" s="2">
+        <v>2</v>
+      </c>
+      <c r="G60" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A61">
+        <v>3</v>
+      </c>
+      <c r="C61" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D61" s="3">
+        <f>_xlfn.POISSON.DIST(A61,G:G,C61)</f>
+        <v>1.0336050675925718E-2</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F61" s="2">
+        <v>5</v>
+      </c>
+      <c r="G61" s="2">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>